--- a/downloads/poc-selection-tool.xlsx
+++ b/downloads/poc-selection-tool.xlsx
@@ -2097,7 +2097,7 @@
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>20â€“24: Pilot candidate. Write the boundary down: who can use it, what it may do, which actions need review, and who can stop it. Then run a limited trial against that boundary.</t>
+          <t>20–24: Pilot candidate. Write the boundary down: who can use it, what it may do, which actions need review, and who can stop it. Then run a limited trial against that boundary.</t>
         </is>
       </c>
       <c r="B28" s="1" t="n"/>
@@ -2109,7 +2109,7 @@
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>14â€“19: Narrow it, then score again. The action list is usually too wide. Remove permitted actions until the low-scoring rows move. A smaller agent that ships beats a broad one that stalls.</t>
+          <t>14–19: Narrow it, then score again. The action list is usually too wide. Remove permitted actions until the low-scoring rows move. A smaller agent that ships beats a broad one that stalls.</t>
         </is>
       </c>
       <c r="B29" s="1" t="n"/>
@@ -2121,7 +2121,7 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>0â€“13: A demo, not a pilot. Not a bad idea. A bad first idea. Build it to learn if you want, but keep it off the roadmap and away from customers.</t>
+          <t>0–13: A demo, not a pilot. Not a bad idea. A bad first idea. Build it to learn if you want, but keep it off the roadmap and away from customers.</t>
         </is>
       </c>
       <c r="B30" s="1" t="n"/>

--- a/downloads/poc-selection-tool.xlsx
+++ b/downloads/poc-selection-tool.xlsx
@@ -50,7 +50,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,8 +126,26 @@
       <color rgb="00183D32"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Source Serif 4"/>
+      <b val="1"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Figtree"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Figtree"/>
+      <b val="1"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +174,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E5EBE1"/>
         <bgColor rgb="00E5EBE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00183D32"/>
+        <bgColor rgb="00183D32"/>
       </patternFill>
     </fill>
   </fills>
@@ -195,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -254,6 +278,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2239,7 +2272,11 @@
       <c r="F40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n"/>
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>The Living Craft cohort</t>
+        </is>
+      </c>
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="n"/>
       <c r="D41" s="1" t="n"/>
@@ -2247,7 +2284,11 @@
       <c r="F41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n"/>
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Test the idea before you widen the pilot. Explore The Living Craft’s October 2026 cohort: 30 live hours with Sunil Mathew, plus independent work.</t>
+        </is>
+      </c>
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="1" t="n"/>
       <c r="D42" s="1" t="n"/>
@@ -2255,7 +2296,11 @@
       <c r="F42" s="1" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n"/>
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Apply at https://learning.thelivingcraft.ai/#apply</t>
+        </is>
+      </c>
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="n"/>
       <c r="D43" s="1" t="n"/>
@@ -3520,10 +3565,13 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
